--- a/Unified_PDF_Platform/unified_outputs/Anthem BC CA CMPLA LLC Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/Anthem BC CA CMPLA LLC Feb-25 Inv_invoice.xlsx
@@ -546,7 +546,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>227/W17126</t>
+          <t>227W17126</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
